--- a/관리/RAG_임베딩모델_비교분석표.xlsx
+++ b/관리/RAG_임베딩모델_비교분석표.xlsx
@@ -7,9 +7,10 @@
     <sheet name="실측_실행비용" sheetId="3" r:id="rId3"/>
     <sheet name="차원분석" sheetId="4" r:id="rId4"/>
     <sheet name="API모델사양" sheetId="5" r:id="rId5"/>
-    <sheet name="판단기준" sheetId="6" r:id="rId6"/>
-    <sheet name="측정이력" sheetId="7" r:id="rId7"/>
-    <sheet name="남은확인" sheetId="8" r:id="rId8"/>
+    <sheet name="라이선스_배포무게" sheetId="6" r:id="rId6"/>
+    <sheet name="판단기준" sheetId="7" r:id="rId7"/>
+    <sheet name="측정이력" sheetId="8" r:id="rId8"/>
+    <sheet name="남은확인" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -238,7 +239,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">실측 최고가 1024 이고, 후보 4종 중 셋이 1024 를 지원한다</t>
+          <t xml:space="preserve">실측 최고가 1024 이고, 후보 API 넷이 모두 1024 를 낼 수 있다</t>
         </is>
       </c>
     </row>
@@ -306,298 +307,332 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">셋 다 다국어이고 한국어 성능을 재지 않았다</t>
+          <t xml:space="preserve">셋 다 다국어이고 한국어 성능을 재지 않았다. 잴 도구는 붙여 뒀다</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">라이선스</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세 모델 전부 MIT — 확인 완료</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KURE · bge-m3 · e5 모두 MIT. 상업적 사용 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">모델 확정</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">보류</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">KURE 와 bge 는 R@5 1문항 차이. 표본 34개에서 노이즈 범위</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13"/>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">그래서 왜 이 결론인가 — 근거 넷</t>
         </is>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">번호</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">확인한 것</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">무엇을 뜻하나</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">1024 차원이 384·768 을 크게 앞섰다</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1024 는 23~27개 · 768 은 13개 · 384 는 14개. 컬럼 차원을 1024 로 두는 1차 근거다</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">차원이 높으면 좋다는 것은 성립하지 않는다</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384 를 768 로 두 배 올렸는데 점수가 내려갔다 (14 → 13). top10 까지 보면 24 → 18 로 6문항 차이다. 차원은 상한만 정하고 실제 성능은 계열과 학습이 정한다</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국어 특화가 효과 있다</t>
+          <t xml:space="preserve">차원이 높으면 좋다는 것은 성립하지 않는다</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">차원을 1024 로 고정하고 계열만 바꾸니 한국어 특화 27 대 다국어 원본 23 으로 4문항 차이다. R@3 에서는 22 대 16 으로 6문항이다</t>
+          <t xml:space="preserve">384 를 768 로 두 배 올렸는데 점수가 내려갔다 (14 → 13). top10 까지 보면 24 → 18 로 6문항 차이다. 차원은 상한만 정하고 실제 성능은 계열과 학습이 정한다</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한국어 특화가 효과 있다</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">차원을 1024 로 고정하고 계열만 바꾸니 한국어 특화 27 대 다국어 원본 23 으로 4문항 차이다. R@3 에서는 22 대 16 으로 6문항이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그래서 다국어 API 로 갈 근거가 약해졌다</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Voyage · OpenAI · Gemini 셋 다 다국어이고 한국어 특화가 아니다. 다국어가 한국어 특화를 이기지 못한 사례를 직접 만들었으므로 문서 전량을 외부로 보낼 근거가 약하다</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="20"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">주의 — 이 표를 잘못 읽는 방법</t>
         </is>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">잘못된 읽기</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">왜 틀렸나</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">맞는 읽기</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API 모델은 쓸 필요 없다</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우리는 API 를 재지 않았다. e5-large 한 개로 다국어 전체를 판단할 수 없다. 그 모델들은 e5-large 보다 크고 최신이다</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재보지 않고 배제하는 것도 근거 없는 판단이다. 2라운드로 남긴다</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">API 모델은 쓸 필요 없다</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리는 API 를 재지 않았다. e5-large 한 개로 다국어 전체를 판단할 수 없다. 그 모델들은 e5-large 보다 크고 최신이다</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재보지 않고 배제하는 것도 근거 없는 판단이다. 2라운드로 남긴다</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">KURE-v1 이 최고 모델이다</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">bge-m3 와 1문항 차이다. R@1 에서는 e5-large 가 14 로 1위다</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">top5 를 보여주는 화면이라 R@5 기준이 맞다. 1건만 보여주면 판단이 달라진다</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384 는 나쁜 차원이다</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384 모델이 글자겹침 질의에서는 38/39 로 1위였다</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">차원이 아니라 용도가 다르다. 뜻으로 찾는 데 약하다</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">384 는 나쁜 차원이다</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384 모델이 글자겹침 질의에서는 38/39 로 1위였다</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">차원이 아니라 용도가 다르다. 뜻으로 찾는 데 약하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">비용 때문에 로컬을 골랐다</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API 비용은 100문서당 $0.06~0.15 다. 무시할 수준이다</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voyage 는 voyage-4 계열에 첫 2억 토큰을 무료로 준다. 우리 규모(문서 2만 건까지)는 무료 구간 안이다</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">쟁점은 비용이 아니라 문서가 외부로 나가는 것이다</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬은 공짜다</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">호출 비용은 0원이지만 배포 무게가 생긴다. torch 와 모델 파일이 들어온다. 지금 Tasqra 의 AI 의존은 openai 한 줄뿐이다</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이것이 API 를 선호할 실질적 이유다 — 라이선스_배포무게 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">이 결론으로 할 수 있는 것</t>
         </is>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">할 일</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">내용</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">선행 조건</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리비전 0011</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CREATE EXTENSION vector · document_chunks embedding vector(1024)</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DB 이미지를 pgvector 포함본으로 교체 (팀 합의 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">requirements.txt</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pgvector 패키지 추가</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SQLAlchemy 에서 Vector 타입을 쓰려면 필요하다</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">리비전 0011</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CREATE EXTENSION vector · document_chunks embedding vector(1024)</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DB 이미지를 pgvector 포함본으로 교체 (팀 합의 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pgvector 패키지 추가</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SQLAlchemy 에서 Vector 타입을 쓰려면 필요하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">검색 API 구현</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">POST /api/projects/{id}/search · mode=hybrid</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">계약 초안은 관리/API_계약_RAG_검색_초안.md</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="34"/>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">수치의 원본은 도구/embed-test/results/ 의 CSV 이고, 판단 근거 전문은 관리/RAG_임베딩모델_선정_결과서.md 다.</t>
         </is>
@@ -1835,7 +1870,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">후보 4종 중 셋이 1024 를 지원한다 — 로컬 한국어 모델 · Voyage(기본값) · OpenAI large(임의 지정). Gemini 만 1024 가 없다</t>
+          <t xml:space="preserve">후보 넷이 모두 1024 를 낼 수 있다 — 로컬 한국어 모델(고정) · Voyage(기본값) · OpenAI large(임의 지정) · Gemini(임의 지정이지만 권장 밖이라 직접 정규화)</t>
         </is>
       </c>
     </row>
@@ -1966,7 +2001,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국어</t>
+          <t xml:space="preserve">무료 구간</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1978,7 +2013,7 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">voyage-3.5</t>
+          <t xml:space="preserve">voyage-4</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2003,19 +2038,19 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">다국어</t>
+          <t xml:space="preserve">첫 2억 토큰</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024 가 기본이라 컬럼을 안 바꾸고 비교할 수 있다</t>
+          <t xml:space="preserve">1024 가 기본이라 컬럼을 안 바꾸고 비교할 수 있다. 2라운드 첫 후보</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">voyage-3.5-lite</t>
+          <t xml:space="preserve">voyage-4-lite</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -2040,56 +2075,56 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">다국어</t>
+          <t xml:space="preserve">첫 2억 토큰</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 차원에 더 싸다</t>
+          <t xml:space="preserve">같은 차원에 더 싸다. 4 계열은 벡터 공간이 서로 호환된다</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text-embedding-3-large</t>
+          <t xml:space="preserve">voyage-4-large</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAI</t>
+          <t xml:space="preserve">Voyage AI (MongoDB)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">256~3072 임의 지정 (기본 3072)</t>
+          <t xml:space="preserve">256 · 512 · 1024(기본) · 2048</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8,192</t>
+          <t xml:space="preserve">32,000</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">$0.13</t>
+          <t xml:space="preserve">$0.12</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">다국어</t>
+          <t xml:space="preserve">첫 2억 토큰</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024 로 줄여서 쓸 수 있다</t>
+          <t xml:space="preserve">MoE 구조. 검색 품질 우선</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text-embedding-3-small</t>
+          <t xml:space="preserve">text-embedding-3-large</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2099,7 +2134,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">512 · 1536</t>
+          <t xml:space="preserve">256~3072 임의 지정 (기본 3072)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2109,226 +2144,236 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">$0.02</t>
+          <t xml:space="preserve">$0.13</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">다국어</t>
+          <t xml:space="preserve">없다</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024 를 지원하지 않는다</t>
+          <t xml:space="preserve">1024 로 줄여서 쓸 수 있다. 질의·문서 구분 파라미터가 없다</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">text-embedding-3-small</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAI</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">512 · 1536</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8,192</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$0.02</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없다</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1024 를 지원하지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gemini-embedding-001</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128~3072 임의 (권장 768·1536·3072)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8,192</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 $0.15</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무료 등급 있음</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1024 를 줄 수 있으나 권장 밖이라 잘린 벡터를 직접 정규화해야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">gemini-embedding-2</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Google</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768 · 1536 · 3072</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8,192</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$0.15</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다국어</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1024 가 없다 · Preview · 멀티모달</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3072 기본 (128~3072 축소 가능)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8,192 (+이미지·영상·음성)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 $0.15~0.20</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무료 등급 있음</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">멀티모달. PDF 직접 입력은 OCR 검수를 무력화하므로 쓰지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">비교 — 로컬 실측치를 같은 축에 놓으면</t>
         </is>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">구분</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">모델</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">지원 차원</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">최대 입력 토큰</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">비용</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">한국어 실측</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">로컬 · 실측</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">KURE-v1</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1024 고정</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">미실측</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0원 · CPU 40초/100청크</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">27 / 34</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로컬 · 실측</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bge-m3</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1024 고정</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미실측</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0원 · CPU 41초/100청크</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26 / 34</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API · 미실측</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voyage-3.5</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1024 기본</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32,000</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$0.06 / 1M 토큰</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모른다</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">API · 미실측</t>
+          <t xml:space="preserve">로컬 · 실측</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text-embedding-3-large</t>
+          <t xml:space="preserve">bge-m3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024 로 지정 가능</t>
+          <t xml:space="preserve">1024 고정</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8,192</t>
+          <t xml:space="preserve">미실측</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">$0.13 / 1M 토큰</t>
+          <t xml:space="preserve">0원 · CPU 41초/100청크</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">모른다</t>
+          <t xml:space="preserve">26 / 34</t>
         </is>
       </c>
     </row>
@@ -2340,297 +2385,450 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gemini-embedding-2</t>
+          <t xml:space="preserve">voyage-4</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">768 · 1536 · 3072</t>
+          <t xml:space="preserve">1024 기본</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">32,000</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">첫 2억 토큰 무료 · 이후 $0.06/1M</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API · 미실측</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text-embedding-3-large</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1024 로 지정 가능</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">8,192</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$0.15 / 1M 토큰</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$0.13 / 1M 토큰</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">모른다</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API · 미실측</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gemini-embedding-001</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1024 가능 (권장 밖)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8,192</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 $0.15 / 1M 토큰</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">비용이 실제로 얼마인가 — 우리 규모로 환산</t>
         </is>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">기준</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">토큰 추정</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voyage-3.5</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voyage-4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">text-embedding-3-large</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서 5건 (이번 시험 코퍼스)</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">약 5만 토큰</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$0.003</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$0.007</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서 100건</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">약 100만 토큰</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$0.06</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$0.13</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">문서 5건 (이번 시험 코퍼스)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 5만 토큰</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무료 구간</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$0.007</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 100건</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 100만 토큰</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무료 구간</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">문서 1,000건</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">약 1,000만 토큰</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$0.60</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무료 구간</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">$1.30</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">토큰 추정은 청크 127개 · 평균 400자 기준의 어림이다. 한국어는 토크나이저에 따라 글자당 0.7~1.5 토큰으로 갈린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비용은 쟁점이 아니다. 문서 1,000건을 다 임베딩해도 1달러 안이다.</t>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 20,000건</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 2억 토큰</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무료 구간의 끝</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$26</t>
         </is>
       </c>
     </row>
     <row r="29"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그러면 진짜 쟁점은 무엇인가</t>
-        </is>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voyage 는 voyage-4 계열에 계정당 첫 2억 토큰을 무료로 준다. 우리 규모는 그 안에 다 들어간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토큰 추정은 청크 127개 · 평균 400자 기준의 어림이다. 한국어는 토크나이저에 따라 글자당 0.7~1.5 토큰으로 갈린다. 가격과 무료 구간은 제공자 문서를 읽은 값이고 우리가 청구서로 확인한 것이 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그러면 진짜 쟁점은 무엇인가 — 비용이 아니다</t>
+        </is>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">쟁점</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어느 쪽이 불리한가</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서가 외부로 나간다</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임베딩은 문서 전량을 보낸다. 요약은 사용자가 요청한 1건만 보내지만 임베딩은 업로드된 모든 문서가 대상이다. 입찰·계약 문서다</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색할 때마다 외부 호출</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">질의도 임베딩해야 한다. 네트워크 지연과 장애가 검색 기능에 그대로 온다. 로컬은 그런 의존이 없다</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한국어 성능을 모른다</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우리 실측에서 다국어 원본이 한국어 특화에 4문항 뒤졌다. API 모델도 다국어다. 재보지 않으면 알 수 없다</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gemini 멀티모달은 쓰면 안 된다</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDF 를 직접 넣으면 사람이 고친 OCR 텍스트가 반영되지 않는다. OCR 검수가 우리 차별점인데 그것을 무력화한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2라운드로 남기는 것</t>
-        </is>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+          <t xml:space="preserve">문서가 외부로 나간다</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 가 불리</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임베딩은 문서 전량을 보낸다. 요약은 사용자가 요청한 1건만 보내지만 임베딩은 업로드된 모든 문서가 대상이다. 입찰·계약 문서다</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색할 때마다 외부 호출</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 가 불리</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">질의도 임베딩해야 한다. 네트워크 지연과 장애가 검색 기능에 그대로 온다. 로컬은 그런 의존이 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한국어 성능을 모른다</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 가 불리</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리 실측에서 다국어 원본이 한국어 특화에 4문항 뒤졌다. API 모델도 다국어다. 재보지 않으면 알 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">배포 무게 — 허깅페이스 의존</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬이 불리</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 모델은 허깅페이스에서 받는다. torch · transformers 가 requirements 에 새로 들어오고 모델 파일도 받아야 한다. 지금 Tasqra 의 AI 의존은 openai 한 줄뿐이다 — 차원분석 옆 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gemini 멀티모달 입력</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쓰지 않는다</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF 를 직접 넣으면 사람이 고친 OCR 텍스트가 반영되지 않는다. OCR 검수가 우리 차별점인데 그것을 무력화한다. 텍스트만 넣는다면 이 문제는 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2라운드 — 지금 실행할 수 있게 만들어 뒀다</t>
+        </is>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">순서</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">무엇을</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">왜 그 순서인가</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">데이터 유출 허용 여부를 팀에서 정한다</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">이것이 안 되면 성능을 재도 못 쓴다</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voyage-3.5 를 우리 질의 73개로 재본다</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1024 가 기본이라 컬럼을 안 바꾸고 비교된다</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voyage-4 를 우리 질의 73개로 재본다</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1024 가 기본이라 컬럼을 안 바꾸고 비교된다. 첫 2억 토큰이 무료라 돈이 안 든다</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gemini-embedding-001 을 1024 로 재본다</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">권장 차원이 아니라 잘린 벡터다. 정규화를 우리가 해야 하고 권장 768 과도 비교해 봐야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">이겨야 얼마나 이기는지 본다</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">KURE 27 을 못 넘으면 볼 이유가 없다</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">출처 — docs.voyageai.com/docs/embeddings · developers.openai.com/api/docs/guides/embeddings · deepmind.google/models/gemini/embedding/ (2026-08 확인)</t>
+    <row r="47"/>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실행 방법 — 도구/embed-test 에 붙여 뒀다. 키를 환경변수로 주고 run_eval.py --api-only 를 돌리면 로컬과 같은 표로 나온다. 키 없이 요청 형식만 검사하려면 check_api_encoders.py 를 돌린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">출처 — docs.voyageai.com/docs/pricing · docs.voyageai.com/reference/embeddings-api-1 · ai.google.dev/gemini-api/docs/embeddings · developers.googleblog.com (2026-08-12 확인). 가격과 무료 구간은 바뀔 수 있다.</t>
         </is>
       </c>
     </row>
@@ -2640,6 +2838,526 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라이선스와 배포 무게 — 허깅페이스 얘기가 나오는 자리</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성능이 같아도 이 두 가지로 판단이 갈릴 수 있다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라이선스 — GitHub REST API 로 확인했다 (2026-08-12)</t>
+        </is>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모델</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저장소</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라이선스</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상업적 사용</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KURE-v1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">github.com/nlpai-lab/KURE</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가능</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gh api repos/nlpai-lab/KURE/license — LICENSE 파일 존재</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bge-m3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">github.com/FlagOpen/FlagEmbedding</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가능</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gh api repos/FlagOpen/FlagEmbedding — 모델 카드도 mit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">multilingual-e5 (base·large)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">github.com/microsoft/unilm</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가능</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gh api repos/microsoft/unilm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e5-small-ko-v2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dragonkue/multilingual-e5-small-ko-v2 (HF)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미확인</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미확인</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384 차원을 기각했으므로 확인하지 않았다. 쓰려면 확인해야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리가 쓰려는 세 모델은 전부 MIT 다. 과제 제출물에 문제 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모델 카드(허깅페이스)와 원본 저장소(GitHub)의 라이선스가 다를 수 있다. 위는 GitHub 저장소를 확인한 값이다. 이 샌드박스에서 허깅페이스 접속이 막혀 모델 카드는 직접 못 봤다. 최종 제출 전에 모델 카드도 한 번 보는 것이 안전하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왜 허깅페이스 얘기가 나오나 — 코드로 확인한 사실</t>
+        </is>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인한 것</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리 시험 도구가 무엇을 쓰나</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sentence-transformers. SentenceTransformer("nlpai-lab/KURE-v1") 의 그 문자열이 허깅페이스 저장소 경로다. 모델 5개 전부 허깅페이스에서 받았다</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tasqra 본코드에 허깅페이스가 있나</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없다. transformers · sentence-transformers · torch 가 requirements.txt 에 하나도 없다. AI 의존은 openai 한 줄뿐이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 LLM 은 허깅페이스를 쓰나</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아니다. app/ai/local_client.py 는 Ollama 의 OpenAI 호환 엔드포인트를 부른다. 허깅페이스와 무관하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그래서 로컬 임베딩을 택하면 Tasqra 에 없던 의존이 새로 들어온다. 이것이 API 를 선호하는 실질적 이유가 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬을 택하면 새로 들어오는 것</t>
+        </is>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">항목</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무엇이</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왜 부담인가</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">패키지</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sentence-transformers → torch · transformers · tokenizers 등</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">torch 는 파이썬 패키지 중 가장 무거운 축이다. 컨테이너 이미지가 커지고 빌드가 느려진다</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모델 파일</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KURE-v1 · bge-m3 는 XLM-R large 계열 (약 5.7억 파라미터)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지에 넣으면 이미지가 커지고, 런타임에 받으면 허깅페이스가 죽으면 앱이 못 뜬다</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메모리</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실측 1,534MB (모델 적재 후 증가분)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이 값은 우리가 쟀다. 컨테이너 메모리 상한을 올려야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기동 시간</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실측 적재 6.4초 (캐시가 이미 있는 상태)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐시가 없으면 내려받는 시간이 더 붙는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">용량을 정확히 재는 방법 — 아직 안 쟀다</t>
+        </is>
+      </c>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무엇을</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">명령 (PowerShell · 보현님 로컬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">허깅페이스 캐시 전체</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"{0:N0} MB" -f ((Get-ChildItem "$env:USERPROFILE\.cache\huggingface" -Recurse -File | Measure-Object Length -Sum).Sum / 1MB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모델별로 나눠서</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get-ChildItem "$env:USERPROFILE\.cache\huggingface\hub" -Directory | ForEach-Object { "{0}  {1:N0} MB" -f $_.Name, ((Get-ChildItem $_ -Recurse -File | Measure-Object Length -Sum).Sum / 1MB) }</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가상환경 (torch 포함)</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"{0:N0} MB" -f ((Get-ChildItem C:\dev\embed-test\.venv -Recurse -File | Measure-Object Length -Sum).Sum / 1MB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위 숫자가 나오면 이 시트를 채운다. 지금은 추측하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이 부담을 줄이는 방법 — 로컬로 가더라도</t>
+        </is>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방법</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내용</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대가</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모델을 이미지에 미리 넣는다</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빌드 때 내려받아 굽는다. 런타임에 허깅페이스를 안 부른다</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지가 커진다. 모델을 바꾸면 다시 빌드해야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">볼륨에 캐시를 마운트한다</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HF_HOME 을 볼륨으로 두면 컨테이너를 다시 만들어도 유지된다</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">볼륨을 팀원마다 채워야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임베딩만 별 컨테이너로 뺀다</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">본 API 는 가볍게 두고 임베딩 서버에 HTTP 로 부른다. Ollama 를 쓰는 지금 구조와 같은 모양이다</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">컨테이너가 하나 늘고 그것도 관리 대상이 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ONNX 로 바꿔 torch 를 뺀다</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">onnxruntime 만 두면 torch 를 안 넣어도 된다</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변환 작업이 붙고 정확도를 다시 확인해야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판단하지 않는다. 배포는 이 시험의 범위가 아니고 팀 결정이다. 다만 로컬이 0원이라는 말이 배포 무게까지 0이라는 뜻은 아니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.2" right="0.2" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -2749,7 +3467,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">비용</t>
+          <t xml:space="preserve">호출 비용</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2764,278 +3482,305 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100문서당 $0.06~0.15</t>
+          <t xml:space="preserve">Voyage 는 첫 2억 토큰 무료 = 문서 약 2만 건</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">비용은 쟁점이 아니다. 둘 다 무시할 수준</t>
+          <t xml:space="preserve">비용은 쟁점이 아니다. 우리 규모는 양쪽 다 0원</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 시 외부 의존</t>
+          <t xml:space="preserve">배포 무게</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색이 멈추면 기능이 죽는다</t>
+          <t xml:space="preserve">컨테이너 이미지와 기동 시간</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">없다</t>
+          <t xml:space="preserve">torch · transformers 가 새로 들어오고 모델 파일도 받아야 한다</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">질의마다 외부 호출. 지연·장애가 그대로 온다</t>
+          <t xml:space="preserve">requirements 에 줄 하나 없이 HTTP 호출만 한다</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">로컬이 유리하다</t>
+          <t xml:space="preserve">API 가 크게 유리하다. 지금 requirements 에 torch 가 없다</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">최대 입력 길이</t>
+          <t xml:space="preserve">검색 시 외부 의존</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">청크가 한도를 넘으면 조용히 잘린다</t>
+          <t xml:space="preserve">검색이 멈추면 기능이 죽는다</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">미실측 — 확인 필요</t>
+          <t xml:space="preserve">없다</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8,192 ~ 32,000 (문서 기준)</t>
+          <t xml:space="preserve">질의마다 외부 호출. 지연·장애가 그대로 온다</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리 청크는 450자라 아직 문제 없어 보이지만 재지 않았다</t>
+          <t xml:space="preserve">로컬이 유리하다</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">차원 유연성</t>
+          <t xml:space="preserve">최대 입력 길이</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">컬럼을 바꾸면 재임베딩이다</t>
+          <t xml:space="preserve">청크가 한도를 넘으면 조용히 잘린다</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">모델마다 고정</t>
+          <t xml:space="preserve">미실측 — 확인 필요</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">임의 지정 가능 (OpenAI)</t>
+          <t xml:space="preserve">8,192 ~ 32,000 (문서 기준)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024 로 맞추면 양쪽 다 가능하다</t>
+          <t xml:space="preserve">우리 청크는 450자라 아직 문제 없어 보이지만 재지 않았다</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">교체 비용</t>
+          <t xml:space="preserve">차원 유연성</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">판단이 틀렸을 때</t>
+          <t xml:space="preserve">컬럼을 바꾸면 재임베딩이다</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">차원 같으면 재임베딩 없음</t>
+          <t xml:space="preserve">모델마다 고정</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">같음</t>
+          <t xml:space="preserve">임의 지정 가능 (OpenAI)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024 를 택한 이유다</t>
+          <t xml:space="preserve">1024 로 맞추면 양쪽 다 가능하다</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">GPU 필요 여부</t>
+          <t xml:space="preserve">교체 비용</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리 개발기에 GPU 가 없다</t>
+          <t xml:space="preserve">판단이 틀렸을 때</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CPU 로 돌아간다 (실측)</t>
+          <t xml:space="preserve">차원 같으면 재임베딩 없음</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">필요 없다</t>
+          <t xml:space="preserve">같음</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">둘 다 문제 없다</t>
+          <t xml:space="preserve">1024 를 택한 이유다</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">GPU 필요 여부</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리 개발기에 GPU 가 없다</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPU 로 돌아간다 (실측)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필요 없다</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">둘 다 문제 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">라이선스</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">과제 제출물이다</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미확인 — 확인 필요</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상용 API 약관</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로컬 모델 라이선스를 확인해야 한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT — 확인 완료 (KURE-v1 · bge-m3 · e5 전부)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상용 API 약관. 데이터 학습 이용 여부를 봐야 한다</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬은 문제 없다. 셋 다 MIT 라 상업적 사용도 가능하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">기각한 선택지와 이유</t>
         </is>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">기각한 것</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">왜 기각했나</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384 차원 모델을 쓴다</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">속도가 11배 빠르지만 뜻으로 찾는 성능이 절반이다. 우리 목적이 의미 검색이다</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">768 로 컬럼을 줄인다</t>
+          <t xml:space="preserve">384 차원 모델을 쓴다</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">저장 용량이 줄지만 실측이 384 보다도 낮았다. Voyage 와 로컬 한국어 모델도 못 쓰게 된다</t>
+          <t xml:space="preserve">속도가 11배 빠르지만 뜻으로 찾는 성능이 절반이다. 우리 목적이 의미 검색이다</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3072 으로 크게 잡는다</t>
+          <t xml:space="preserve">768 로 컬럼을 줄인다</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">저장이 3배로 늘고 이 차원을 내는 로컬 모델이 없다. API 에 묶인다</t>
+          <t xml:space="preserve">저장 용량이 줄지만 실측이 384 보다도 낮았다. Voyage 와 로컬 한국어 모델도 못 쓰게 된다</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">API 모델을 즉시 배제한다</t>
+          <t xml:space="preserve">3072 으로 크게 잡는다</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리가 잰 다국어 모델은 e5-large 하나다. API 모델들은 그보다 크고 최신이라 배제할 근거가 없다</t>
+          <t xml:space="preserve">저장이 3배로 늘고 이 차원을 내는 로컬 모델이 없다. API 에 묶인다</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">지금 API 모델을 도입한다</t>
+          <t xml:space="preserve">API 모델을 즉시 배제한다</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 전량이 외부로 나간다. 그 결정을 성능 근거 없이 할 수 없다</t>
+          <t xml:space="preserve">우리가 잰 다국어 모델은 e5-large 하나다. API 모델들은 그보다 크고 최신이라 배제할 근거가 없다</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">결과를 문서 단위로 묶는다</t>
+          <t xml:space="preserve">지금 API 모델을 도입한다</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거 스니펫에 원문을 인용해야 하는데 문서로 묶으면 그것이 사라진다. 결과 단위는 청크로 둔다</t>
+          <t xml:space="preserve">문서 전량이 외부로 나간다. 그 결정을 성능 근거 없이 할 수 없다</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">결과를 문서 단위로 묶는다</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근거 스니펫에 원문을 인용해야 하는데 문서로 묶으면 그것이 사라진다. 결과 단위는 청크로 둔다</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">임베딩을 비동기로 만든다</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">작업 큐가 아직 없고 업로드·분석이 이미 동기다. 일관성을 택했다</t>
         </is>
@@ -3046,7 +3791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -3338,7 +4083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -3382,17 +4127,17 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">로컬 모델 라이선스</t>
+          <t xml:space="preserve">로컬 모델 파일 용량 실측</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">과제 제출물에 쓸 수 있는지</t>
+          <t xml:space="preserve">컨테이너 이미지가 얼마나 커지는지</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">미확인. KURE-v1 · bge-m3 둘 다 봐야 한다</t>
+          <t xml:space="preserve">미확인. 보현님 로컬의 허깅페이스 캐시를 재면 나온다 (라이선스 시트에 명령)</t>
         </is>
       </c>
     </row>
@@ -3477,101 +4222,166 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">안 했다. 데이터 유출 허용 여부가 선행 판단이다</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+          <t xml:space="preserve">안 했다. 하네스는 붙여 뒀다. 데이터 유출 허용 여부가 선행 판단이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 약관의 데이터 이용 조항</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리 문서가 학습에 쓰이는지</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미확인. 유출을 허용하기로 하면 이것을 먼저 읽어야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">확인한 것 — 코드로 본 값이다</t>
         </is>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">확인 대상</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">결과</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DB 이미지에 pgvector 가 있나</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">없다. docker-compose.yml 이 postgres:16-alpine 이다</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">마이그레이션에 CREATE EXTENSION vector 가 있나</t>
+          <t xml:space="preserve">DB 이미지에 pgvector 가 있나</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">없다. 리비전 0001~0009 전체를 봤다</t>
+          <t xml:space="preserve">없다. docker-compose.yml 이 postgres:16-alpine 이다</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">requirements.txt 에 pgvector 가 있나</t>
+          <t xml:space="preserve">마이그레이션에 CREATE EXTENSION vector 가 있나</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">없다</t>
+          <t xml:space="preserve">없다. 리비전 0001~0009 전체를 봤다</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업 큐(celery·redis)가 있나</t>
+          <t xml:space="preserve">requirements.txt 에 pgvector 가 있나</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">없다. 코드에 매치 0건이다. 그래서 임베딩도 동기로 간다</t>
+          <t xml:space="preserve">없다</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">작업 큐(celery·redis)가 있나</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없다. 코드에 매치 0건이다. 그래서 임베딩도 동기로 간다</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">리비전 head 가 무엇인가</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">20260812_0009 (extracted_char_sources). 보현 몫은 0010 · 0011 이다</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">CHECK 제약 명명 선례가 있나</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">있다. 0009 가 ck_extracted_text_char_count 를 썼다. ck_{테이블단수}_{컬럼} 형태를 따른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 모델 라이선스</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KURE-v1 · bge-m3 · e5 전부 MIT. GitHub REST API 로 확인했다</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tasqra 에 허깅페이스 의존이 있나</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없다. torch · transformers 가 requirements.txt 에 하나도 없다. 로컬 임베딩을 택하면 새로 들어온다</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 LLM 이 허깅페이스를 쓰나</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아니다. local_client.py 는 Ollama 의 OpenAI 호환 API 를 부른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gemini 가 1024 를 지원하나</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">된다. outputDimensionality 는 128~3072 다. 다만 권장은 768·1536·3072 이고 그 밖은 잘린 벡터라 직접 정규화해야 한다</t>
         </is>
       </c>
     </row>
